--- a/03_Implement/test/fixtures/libreoffice-fill-impact-family.xlsx
+++ b/03_Implement/test/fixtures/libreoffice-fill-impact-family.xlsx
@@ -844,6 +844,262 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
